--- a/Tables/Example table data.xlsx
+++ b/Tables/Example table data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fikot03\Documents\IEU Files\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C528907-6070-47CC-BEB6-80AFC3F94F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A064597-36FD-49C1-8FF8-3422D797729F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29730" yWindow="1365" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34785" yWindow="4380" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="gt and kable" sheetId="1" r:id="rId1"/>
+    <sheet name="gtsummary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="10">
   <si>
     <t>Group</t>
   </si>
@@ -36,41 +37,47 @@
     <t>N</t>
   </si>
   <si>
-    <t>Group1</t>
+    <t>Group A</t>
   </si>
   <si>
-    <t>2014</t>
+    <t>Group B</t>
   </si>
   <si>
-    <t>Group2</t>
+    <t>Variable1</t>
   </si>
   <si>
-    <t>Group3</t>
+    <t>Variable2</t>
   </si>
   <si>
-    <t>Group4</t>
+    <t>Variable3</t>
   </si>
   <si>
-    <t>Group5</t>
+    <t>Variable4</t>
   </si>
   <si>
-    <t>Group6</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
+    <t>Group C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -96,9 +103,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -379,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -398,204 +409,572 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2014</v>
       </c>
       <c r="C2">
         <v>3998</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2014</v>
       </c>
       <c r="C3">
         <v>1916</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2014</v>
       </c>
       <c r="C4">
         <v>1714</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2015</v>
       </c>
       <c r="C5">
-        <v>1683</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2015</v>
       </c>
       <c r="C6">
-        <v>1477</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>4</v>
+      <c r="B7" s="3">
+        <v>2015</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2016</v>
       </c>
       <c r="C8">
-        <v>4448</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2016</v>
       </c>
       <c r="C9">
-        <v>2024</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2016</v>
       </c>
       <c r="C10">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>1585</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14">
-        <v>4491</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16">
         <v>2111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17">
-        <v>2097</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18">
-        <v>1616</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19">
-        <v>1000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D129B1-08C1-40B8-8A9E-900CDADF76C8}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>20.9</v>
+      </c>
+      <c r="D2" s="1">
+        <v>22.6</v>
+      </c>
+      <c r="E2" s="1">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>20.3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>21.8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>19.7</v>
+      </c>
+      <c r="D4" s="1">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>20.3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E6" s="1">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>20.8</v>
+      </c>
+      <c r="C7" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>21.9</v>
+      </c>
+      <c r="E7" s="1">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1">
+        <v>17.2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>17.2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="E8" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>17.8</v>
+      </c>
+      <c r="C9" s="1">
+        <v>18.8</v>
+      </c>
+      <c r="D9" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D10" s="1">
+        <v>18.8</v>
+      </c>
+      <c r="E10" s="1">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>20.7</v>
+      </c>
+      <c r="D12" s="1">
+        <v>21.4</v>
+      </c>
+      <c r="E12" s="1">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="D13" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="1">
+        <v>18.7</v>
+      </c>
+      <c r="C14" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>21.8</v>
+      </c>
+      <c r="E15" s="1">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1">
+        <v>17.7</v>
+      </c>
+      <c r="C16" s="1">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D16" s="1">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="E16" s="1">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="C17" s="1">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D17" s="1">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="E17" s="1">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="D18" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="D19" s="1">
+        <v>20.7</v>
+      </c>
+      <c r="E19" s="1">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="C20" s="1">
+        <v>20.8</v>
+      </c>
+      <c r="D20" s="1">
+        <v>20.8</v>
+      </c>
+      <c r="E20" s="1">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="C21" s="1">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D21" s="1">
+        <v>19.7</v>
+      </c>
+      <c r="E21" s="1">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="C22" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="D22" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E22" s="1">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="C23" s="1">
+        <v>20.6</v>
+      </c>
+      <c r="D23" s="1">
+        <v>21.4</v>
+      </c>
+      <c r="E23" s="1">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="C24" s="1">
+        <v>19.7</v>
+      </c>
+      <c r="D24" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1">
+        <v>18.8</v>
+      </c>
+      <c r="C25" s="1">
+        <v>20.2</v>
+      </c>
+      <c r="D25" s="1">
+        <v>20.8</v>
+      </c>
+      <c r="E25" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1">
+        <v>20.2</v>
+      </c>
+      <c r="C26" s="1">
+        <v>21.4</v>
+      </c>
+      <c r="D26" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>